--- a/data/attendance.xlsx
+++ b/data/attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I459"/>
+  <dimension ref="A1:I464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18500,10 +18500,8 @@
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E458" t="n">
+        <v>2</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -18542,10 +18540,8 @@
           <t>Charles Byson Gama</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D459" t="n">
+        <v>1</v>
       </c>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr">
@@ -18566,6 +18562,221 @@
       <c r="I459" t="inlineStr">
         <is>
           <t>Main Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>CC0011</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Alexander Muyira</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Weeding</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Bana</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>CC0004</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Meckson James Simon Chigoga</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Weeding</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Capitao</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Bana</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>CC0020</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Henry Lazaro Uzitani</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Weeding</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Chigoga</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Bana</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>CC0091</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Edwin Phiri</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Weeding</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Chigoga</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Bana</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>CC0112</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Petro Davison</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Weeding</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Chigoga</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Bana</t>
         </is>
       </c>
     </row>
